--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T10:56:37+00:00</t>
+    <t>2025-01-17T11:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="344">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T11:40:58+00:00</t>
+    <t>2025-01-21T12:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,13 +656,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Identification of the condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>https://fhir.hl7.at/elga-austrianpatientsummary-r4/ValueSet/at-ips-condition-code-systems</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -960,6 +954,9 @@
   </si>
   <si>
     <t>A simple summary of the stage such as "Stage 3". The determination of the stage is disease-specific.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
@@ -1427,7 +1424,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="85.23828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.15625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="84.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
@@ -3312,13 +3309,11 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3351,30 +3346,30 @@
         <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3400,13 +3395,13 @@
         <v>157</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3435,10 +3430,10 @@
         <v>185</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>79</v>
@@ -3456,7 +3451,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3474,31 +3469,31 @@
         <v>79</v>
       </c>
       <c r="AL17" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AM17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>223</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3517,17 +3512,17 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>79</v>
@@ -3576,7 +3571,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>90</v>
@@ -3591,19 +3586,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>79</v>
@@ -3611,10 +3606,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3637,16 +3632,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3696,7 +3691,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3711,19 +3706,19 @@
         <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>79</v>
@@ -3731,10 +3726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3757,16 +3752,16 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3816,7 +3811,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3831,19 +3826,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>79</v>
@@ -3851,10 +3846,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3877,16 +3872,16 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3936,7 +3931,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3945,7 +3940,7 @@
         <v>90</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>102</v>
@@ -3960,10 +3955,10 @@
         <v>79</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>79</v>
@@ -3971,10 +3966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3997,13 +3992,13 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4054,7 +4049,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4075,13 +4070,13 @@
         <v>79</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>79</v>
@@ -4089,10 +4084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4115,13 +4110,13 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4172,7 +4167,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4196,10 +4191,10 @@
         <v>79</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>79</v>
@@ -4207,10 +4202,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4233,13 +4228,13 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4290,7 +4285,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4311,13 +4306,13 @@
         <v>79</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>79</v>
@@ -4325,10 +4320,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4351,13 +4346,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4408,7 +4403,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4420,7 +4415,7 @@
         <v>79</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>79</v>
@@ -4432,7 +4427,7 @@
         <v>79</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>79</v>
@@ -4443,10 +4438,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4469,13 +4464,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4526,7 +4521,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4550,7 +4545,7 @@
         <v>79</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>79</v>
@@ -4561,10 +4556,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4593,7 +4588,7 @@
         <v>137</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>139</v>
@@ -4646,7 +4641,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4670,7 +4665,7 @@
         <v>79</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>79</v>
@@ -4681,14 +4676,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4710,10 +4705,10 @@
         <v>136</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>139</v>
@@ -4768,7 +4763,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4803,10 +4798,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4832,10 +4827,10 @@
         <v>157</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4862,14 +4857,14 @@
         <v>79</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z29" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA29" t="s" s="2">
         <v>79</v>
       </c>
@@ -4886,7 +4881,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4895,7 +4890,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -4904,13 +4899,13 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>79</v>
@@ -4921,10 +4916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4947,13 +4942,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5004,7 +4999,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5013,7 +5008,7 @@
         <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5028,7 +5023,7 @@
         <v>79</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>79</v>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5068,10 +5063,10 @@
         <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5098,14 +5093,14 @@
         <v>79</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>79</v>
       </c>
@@ -5122,7 +5117,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5146,7 +5141,7 @@
         <v>79</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>79</v>
@@ -5157,10 +5152,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5183,16 +5178,16 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5242,7 +5237,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5254,19 +5249,19 @@
         <v>79</v>
       </c>
       <c r="AJ32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>79</v>
@@ -5277,10 +5272,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5303,13 +5298,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5360,7 +5355,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5384,7 +5379,7 @@
         <v>79</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>79</v>
@@ -5395,10 +5390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5427,7 +5422,7 @@
         <v>137</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>139</v>
@@ -5480,7 +5475,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5504,7 +5499,7 @@
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5515,14 +5510,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5544,10 +5539,10 @@
         <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>139</v>
@@ -5602,7 +5597,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5637,10 +5632,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5666,10 +5661,10 @@
         <v>157</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5696,14 +5691,14 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
       </c>
@@ -5720,7 +5715,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5729,13 +5724,13 @@
         <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>187</v>
@@ -5744,10 +5739,10 @@
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>79</v>
@@ -5755,10 +5750,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5781,13 +5776,13 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5838,7 +5833,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5847,7 +5842,7 @@
         <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>102</v>
@@ -5862,10 +5857,10 @@
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>79</v>
@@ -5873,10 +5868,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5899,13 +5894,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5956,7 +5951,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5971,16 +5966,16 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>79</v>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-21T12:24:15+00:00</t>
+    <t>2025-01-23T11:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T11:46:49+00:00</t>
+    <t>2025-01-24T11:26:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-ips-condition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
